--- a/outputs/evaluation/architecture/validation/CF_M06/run_1/CF_M06_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/validation/CF_M06/run_1/CF_M06_arch_eval.xlsx
@@ -454,7 +454,7 @@
         <v>0.875</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5833</v>
+        <v>0.7778</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -469,13 +469,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.95</v>
+        <v>0.9231</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6552</v>
+        <v>0.8276</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9527</v>
+        <v>0.9572000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -485,13 +485,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5</v>
+        <v>0.6667</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3333</v>
+        <v>0.5714</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.8875</v>
       </c>
     </row>
     <row r="7">
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9048</v>
+        <v>0.8571</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -533,10 +533,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7368</v>
+        <v>0.875</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8584000000000001</v>
+        <v>0.8827</v>
       </c>
     </row>
     <row r="10">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9524</v>
+        <v>0.8929</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2222</v>
+        <v>0.125</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -642,16 +642,16 @@
         <v>24</v>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D2" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0.9048</v>
       </c>
       <c r="F2" t="n">
-        <v>0.625</v>
+        <v>0.7917</v>
       </c>
     </row>
     <row r="3">
@@ -667,13 +667,13 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -686,16 +686,16 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D4" t="n">
         <v>4</v>
       </c>
-      <c r="D4" t="n">
-        <v>2</v>
-      </c>
       <c r="E4" t="n">
-        <v>0.5</v>
+        <v>0.6667</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2857</v>
+        <v>0.5714</v>
       </c>
     </row>
   </sheetData>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5833</v>
+        <v>0.7778</v>
       </c>
     </row>
     <row r="10">
@@ -880,22 +880,22 @@
         <v>29</v>
       </c>
       <c r="C2" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E2" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F2" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G2" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H2" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
@@ -905,25 +905,25 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3" t="n">
         <v>6</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>4</v>
       </c>
-      <c r="D3" t="n">
-        <v>2</v>
-      </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
@@ -936,22 +936,22 @@
         <v>36</v>
       </c>
       <c r="C4" t="n">
+        <v>32</v>
+      </c>
+      <c r="D4" t="n">
+        <v>28</v>
+      </c>
+      <c r="E4" t="n">
+        <v>28</v>
+      </c>
+      <c r="F4" t="n">
+        <v>28</v>
+      </c>
+      <c r="G4" t="n">
         <v>24</v>
       </c>
-      <c r="D4" t="n">
-        <v>21</v>
-      </c>
-      <c r="E4" t="n">
-        <v>21</v>
-      </c>
-      <c r="F4" t="n">
-        <v>21</v>
-      </c>
-      <c r="G4" t="n">
-        <v>19</v>
-      </c>
       <c r="H4" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
@@ -964,22 +964,22 @@
         <v>29</v>
       </c>
       <c r="C5" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E5" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F5" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G5" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="H5" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
@@ -992,22 +992,22 @@
         <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D6" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E6" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F6" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G6" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H6" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7">
@@ -1020,22 +1020,22 @@
         <v>25</v>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8">
@@ -1063,7 +1063,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1077,7 +1077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T22"/>
+  <dimension ref="A1:T29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1341,94 +1341,94 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P_03</t>
+          <t>AU_25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CF_M06_P03</t>
+          <t>CF_M06_AU30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Observer</t>
-        </is>
-      </c>
+        <v>0.8232</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>A design pattern to observe the state of an object in a program, reflected in the Flux architecture where stores act as subjects.</t>
+          <t>The application connects via socket with the server to show content in real time.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>['P_02']</t>
+          <t>['AU_03', 'AU_02']</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>P_03</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Observer Pattern</t>
-        </is>
-      </c>
+          <t>AU_25</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>presentation layer, waapiti server</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>The observer pattern is a design pattern for observing the state of an object in a program.</t>
+          <t>This functionality connects via socket [25] with the server and displays</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>CF_M06_P02</t>
+          <t>CF_M06_AU23, CF_M06_AU02</t>
         </is>
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
-          <t>CF_M06_P03</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr"/>
+          <t>CF_M06_AU30</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>mobile application, waapiti server</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P_04</t>
+          <t>P_03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CF_M06_P04</t>
+          <t>CF_M06_P03</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1437,11 +1437,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.8250999999999999</v>
+        <v>0.825</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Decorator</t>
+          <t>Observer</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1451,25 +1451,25 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>A design pattern that allows adding behavior to an object, used to extend component functionalities for testing.</t>
+          <t>A design pattern to observe the state of an object in a program.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>P_04</t>
+          <t>P_03</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Decorator Pattern</t>
+          <t>Observer Pattern</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1479,21 +1479,21 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>The decorator pattern is a design pattern that allows you to add behavior to an object, both statically and dynamically. In this project, it has been used to facilitate testing tasks.</t>
+          <t>The observer pattern is a design pattern for observing the state of an object in a program.</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>CF_M06_AU23</t>
+          <t>CF_M06_P02</t>
         </is>
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
-          <t>CF_M06_P04</t>
+          <t>CF_M06_P03</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -1501,84 +1501,80 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AU_17</t>
+          <t>P_04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CF_M06_AU30</t>
+          <t>CF_M06_P04</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
+        <v>0.8250999999999999</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Decorator</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Aquesta funcionalitat es connecta via socket amb el servidor i mostra el contingut segons els missatges que aquest envia.</t>
+          <t>A design pattern that allows adding behavior to an object, both statically and dynamically.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>['AU_03', 'AU_02']</t>
-        </is>
-      </c>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>AU_17</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>presentation layer, waapiti server</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>P_04</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Decorator Pattern</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>This functionality connects via socket [25] with the server and displays</t>
+          <t>The decorator pattern is a design pattern that allows you to add behavior to an object, both statically and dynamically. In this project, it has been used to facilitate testing tasks.</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>CF_M06_AU23, CF_M06_AU02</t>
+          <t>CF_M06_AU23</t>
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
-          <t>CF_M06_AU30</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>mobile application, waapiti server</t>
-        </is>
-      </c>
+          <t>CF_M06_P04</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1661,31 +1657,35 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AU_16</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CF_M06_AU27</t>
+          <t>CF_M06_P01</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.925</v>
-      </c>
-      <c r="E8" t="inlineStr"/>
+        <v>0.8697</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Three-layer Architecture</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Aquesta interactuarà amb l’API de Waapiti mitjançant peticions HTTP.</t>
+          <t>This architecture follows the 3-layer model: Presentation, Domain, and Data.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1693,31 +1693,27 @@
           <t>45</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>['AU_03', 'AU_02']</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>AU_16</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>presentation layer, waapiti server</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>P_01</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Three Layers</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>This will interact with the Waapiti API using HTTP requests.</t>
+          <t>This architecture follows the 3-layer model</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -1725,333 +1721,333 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>CF_M06_AU01, CF_M06_AU02</t>
+          <t>CF_M06_AU23</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
-          <t>CF_M06_AU27</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>mobile device, waapiti server</t>
-        </is>
-      </c>
+          <t>CF_M06_P01</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AU_01</t>
+          <t>AU_23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CF_M06_AU01</t>
+          <t>CF_M06_AU10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.9895</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Mobile Device</t>
-        </is>
-      </c>
+        <v>0.8976</v>
+      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Device</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>The physical device where the application is hosted, either iOS or Android.</t>
+          <t>The Dispatcher notifies Stores when the state should be modified.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>['AU_08', 'AU_06']</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>AU_01</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Mobile device</t>
-        </is>
-      </c>
+          <t>AU_23</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>dispatcher, store</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Device</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>This is the device where the application will be hosted.</t>
+          <t>With the data obtained, the Dispatcher notifies the Stores that need to be modified, thus updating the components.</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>45</v>
-      </c>
-      <c r="Q9" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>CF_M06_AU08, CF_M06_AU07</t>
+        </is>
+      </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
-          <t>CF_M06_AU01</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr"/>
+          <t>CF_M06_AU10</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>action, store</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AU_09</t>
+          <t>AU_22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CF_M06_AU06</t>
+          <t>CF_M06_AU28</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>React Native</t>
-        </is>
-      </c>
+        <v>0.9107</v>
+      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Open source development framework used to develop applications for Android and iOS.</t>
+          <t>The Waapiti Server communicates with the database and other services hosted on AWS.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>['AU_03']</t>
+          <t>['AU_02', 'AU_05']</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>AU_09</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>React Native</t>
-        </is>
-      </c>
+          <t>AU_22</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>waapiti server, data layer</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>The framework used in this work is React Native, which runs on React (a framework for creating frontend interfaces).</t>
+          <t>It is the server responsible for communicating with the database and other services hosted on AWS.</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>CF_M06_AU23</t>
+          <t>CF_M06_AU02, CF_M06_AU05</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
-          <t>CF_M06_AU06</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr"/>
+          <t>CF_M06_AU28</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>waapiti server, data</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AU_10</t>
+          <t>AU_21</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CF_M06_AU14</t>
+          <t>CF_M06_AU27</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>React</t>
-        </is>
-      </c>
+        <v>0.9185</v>
+      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Library for building user interfaces using Javascript.</t>
+          <t>The mobile application interacts with the Waapiti API using HTTP requests.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>['AU_09']</t>
+          <t>['AU_03', 'AU_02']</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>AU_10</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>React</t>
-        </is>
-      </c>
+          <t>AU_21</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>presentation layer, waapiti server</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>is a library for building user interfaces using Javascript.</t>
+          <t>This will interact with the Waapiti API using HTTP requests.</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>CF_M06_AU23</t>
+          <t>CF_M06_AU01, CF_M06_AU02</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
-          <t>CF_M06_AU14</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr"/>
+          <t>CF_M06_AU27</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>mobile device, waapiti server</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P_05</t>
+          <t>AU_01</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CF_M06_P05</t>
+          <t>CF_M06_AU01</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0.9895</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lazy Loading</t>
+          <t>Mobile Device</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Device</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>The concept of loading objects/components only when they are necessary.</t>
+          <t>The physical device where the application is hosted, either iOS or Android.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>P_05</t>
+          <t>AU_01</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Lazy Loading</t>
+          <t>Mobile device</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Device</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>The concept of Lazy Loading consists of loading objects/components only when they are needed. In this way, we achieve optimized efficiency. In this project, thanks to the React Navigation library, used to manage the application's navigation, this concept has been implemented.</t>
+          <t>This is the device where the application will be hosted.</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>49</v>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>CF_M06_AU23</t>
-        </is>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
-          <t>CF_M06_P05</t>
+          <t>CF_M06_AU01</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
@@ -2059,12 +2055,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AU_08</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CF_M06_AU09</t>
+          <t>CF_M06_AU06</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2077,59 +2073,59 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dispatcher</t>
+          <t>React Native</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>The central axis that manages the entire data flow and notifies Stores when the state needs to be modified.</t>
+          <t>Open source development framework used to develop applications for Android and iOS.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>51</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>AU_08</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Dispatcher</t>
+          <t>React Native</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>This is the central hub that manages all the data flow.</t>
+          <t>The framework used in this work is React Native, which runs on React (a framework for creating frontend interfaces).</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>CF_M06_P02</t>
+          <t>CF_M06_AU23</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
-          <t>CF_M06_AU09</t>
+          <t>CF_M06_AU06</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -2137,12 +2133,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AU_14</t>
+          <t>AU_10</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CF_M06_AU29</t>
+          <t>CF_M06_AU14</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2155,7 +2151,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>React</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2165,29 +2161,25 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Communication protocol used by the mobile application to interact with the Waapiti API.</t>
+          <t>Library for building user interfaces using Javascript.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>['AU_16']</t>
-        </is>
-      </c>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>AU_14</t>
+          <t>AU_10</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>React</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2197,21 +2189,21 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>This will interact with the Waapiti API using HTTP requests.</t>
+          <t>is a library for building user interfaces using Javascript.</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>CF_M06_AU26</t>
+          <t>CF_M06_AU23</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
-          <t>CF_M06_AU29</t>
+          <t>CF_M06_AU14</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
@@ -2219,17 +2211,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AU_02</t>
+          <t>P_05</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CF_M06_AU02</t>
+          <t>CF_M06_P05</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -2237,55 +2229,59 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Waapiti Server</t>
+          <t>Lazy Loading</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>API of the company that the application consumes, responsible for communicating with the database and other services hosted on AWS.</t>
+          <t>The concept of loading objects/components only when they are necessary.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>49</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>AU_02</t>
+          <t>P_05</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Waapiti Server</t>
+          <t>Lazy Loading</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>API [15] of the company consuming the application. It is the server responsible for communicating with the database and other services hosted on AWS.</t>
+          <t>The concept of Lazy Loading consists of loading objects/components only when they are needed. In this way, we achieve optimized efficiency. In this project, thanks to the React Navigation library, used to manage the application's navigation, this concept has been implemented.</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>45</v>
-      </c>
-      <c r="Q15" t="inlineStr"/>
+        <v>49</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>CF_M06_AU23</t>
+        </is>
+      </c>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
-          <t>CF_M06_AU02</t>
+          <t>CF_M06_P05</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
@@ -2293,12 +2289,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AU_06</t>
+          <t>AU_08</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CF_M06_AU07</t>
+          <t>CF_M06_AU09</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2311,7 +2307,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Dispatcher</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2321,25 +2317,25 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>The component that contains the state and logic of the application.</t>
+          <t>The central axis that manages the entire data flow and notifies Stores when the state should be modified.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>47</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>AU_06</t>
+          <t>AU_08</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Dispatcher</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2349,11 +2345,11 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>This is the component that contains the state and logic of the application.</t>
+          <t>This is the central hub that manages all the data flow.</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2363,7 +2359,7 @@
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
-          <t>CF_M06_AU07</t>
+          <t>CF_M06_AU09</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
@@ -2371,12 +2367,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AU_11</t>
+          <t>AU_12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CF_M06_AU15</t>
+          <t>CF_M06_AU16</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2389,7 +2385,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Expo</t>
+          <t>Jest</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2399,7 +2395,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Open source framework for native Android, iOS, and Web applications.</t>
+          <t>Testing framework for Javascript.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2407,21 +2403,17 @@
           <t>51</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>['AU_09']</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>AU_11</t>
+          <t>AU_12</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Expo</t>
+          <t>Jest</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2431,7 +2423,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>is an open source framework for native Android, iOS and Web applications.</t>
+          <t>is a testing framework for Javascript. It is also the libraryrecommended for React projects. [20]</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -2445,7 +2437,7 @@
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
-          <t>CF_M06_AU15</t>
+          <t>CF_M06_AU16</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
@@ -2453,12 +2445,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AU_12</t>
+          <t>AU_27</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CF_M06_AU25</t>
+          <t>CF_M06_AU29</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2471,7 +2463,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Redux</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2481,29 +2473,29 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Library used to manage the application state.</t>
+          <t>Aquesta interactuarà amb l’API de Waapiti mitjançant peticions HTTP.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>['AU_04']</t>
+          <t>['AU_21']</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>AU_12</t>
+          <t>AU_27</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Redux</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2513,21 +2505,21 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Redux [19] is a library used to manage application state. It is inspired by the Flux architecture, but with a simpler implementation.</t>
+          <t>This will interact with the Waapiti API using HTTP requests.</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>CF_M06_AU23</t>
+          <t>CF_M06_AU26</t>
         </is>
       </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
-          <t>CF_M06_AU25</t>
+          <t>CF_M06_AU29</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
@@ -2535,12 +2527,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AU_13</t>
+          <t>AU_02</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CF_M06_AU22</t>
+          <t>CF_M06_AU02</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2553,55 +2545,55 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS SNS</t>
+          <t>Waapiti Server</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Service used for push notifications.</t>
+          <t>API of the company that the application consumes, responsible for communicating with the database and other services hosted on AWS.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>AU_13</t>
+          <t>AU_02</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>AWS SNS</t>
+          <t>Waapiti Server</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>In the end it was decided to use AWS SNS due to the cost compared to Expo Push API. In addition, AWS SNS is more scalable and can be used by other services.</t>
+          <t>API [15] of the company consuming the application. It is the server responsible for communicating with the database and other services hosted on AWS.</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>92</v>
+        <v>45</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
-          <t>CF_M06_AU22</t>
+          <t>CF_M06_AU02</t>
         </is>
       </c>
       <c r="T19" t="inlineStr"/>
@@ -2609,17 +2601,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P_02</t>
+          <t>AU_06</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CF_M06_P02</t>
+          <t>CF_M06_AU07</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2627,17 +2619,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Flux</t>
+          <t>Store</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>An architecture for managing and flowing data in a web application, designed to replace the Model-View-Controller (MVC) pattern.</t>
+          <t>The component that contains the state and logic of the application.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2649,23 +2641,23 @@
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>P_02</t>
+          <t>AU_06</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Flux</t>
+          <t>Store</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>In this project it has been decided to develop using the Flux architecture [18], introduced by Facebook.</t>
+          <t>This is the component that contains the state and logic of the application.</t>
         </is>
       </c>
       <c r="P20" t="n">
@@ -2673,13 +2665,13 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>CF_M06_AU23</t>
+          <t>CF_M06_P02</t>
         </is>
       </c>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
-          <t>CF_M06_P02</t>
+          <t>CF_M06_AU07</t>
         </is>
       </c>
       <c r="T20" t="inlineStr"/>
@@ -2687,12 +2679,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AU_15</t>
+          <t>AU_11</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CF_M06_AU31</t>
+          <t>CF_M06_AU15</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2705,7 +2697,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Socket</t>
+          <t>Expo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2715,29 +2707,25 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Communication protocol used for real-time updates and logs.</t>
+          <t>Open source framework for native Android, iOS, and Web applications.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>['AU_17', 'AU_18', 'AU_19']</t>
-        </is>
-      </c>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>AU_15</t>
+          <t>AU_11</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Socket</t>
+          <t>Expo</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2747,21 +2735,21 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>the content according to the messages that it sends.</t>
+          <t>is an open source framework for native Android, iOS and Web applications.</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>CF_M06_AU30</t>
+          <t>CF_M06_AU23</t>
         </is>
       </c>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
-          <t>CF_M06_AU31</t>
+          <t>CF_M06_AU15</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
@@ -2769,12 +2757,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AU_07</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CF_M06_AU08</t>
+          <t>CF_M06_AU17</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2787,62 +2775,596 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>NodeJS</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>A Javascript object that indicates an intention to modify the application state.</t>
+          <t>Javascript execution environment used for compiling.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>51</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>AU_07</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>NodeJS</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> is a Javascript object that indicates an intention to modify the state of the application.</t>
+          <t>is a Javascript runtime environment that allows you to run it outside of the browser. In this case it is used to compile.</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>47</v>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>CF_M06_P02</t>
-        </is>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
+          <t>CF_M06_AU17</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>AU_15</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CF_M06_AU19</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>NestJS</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Progressive NodeJS framework for creating efficient, reliable, and scalable backend applications.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>AU_15</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>NestJS</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>is a progressive NodeJS framework for creating efficient applications reliable and scalable backend entities.</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>CF_M06_AU19</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>AU_17</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CF_M06_AU22</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AWS SNS</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Amazon Simple Notification Service used for delivering push notifications.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>['AU_16', 'AU_26']</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>AU_17</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>AWS SNS</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>In the end it was decided to use AWS SNS due to the cost compared to Expo Push API. In addition, AWS SNS is more scalable and can be used by other services.</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>92</v>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>CF_M06_AU22</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>P_02</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CF_M06_P02</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>pattern</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Flux</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Architectural Pattern</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>An architecture for handling and flowing data in a web application, designed to replace the Model-View-Controller (MVC) pattern.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>P_02</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Flux</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Architectural Pattern</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>In this project it has been decided to develop using the Flux architecture [18], introduced by Facebook.</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>46</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>CF_M06_AU23</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>CF_M06_P02</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>AU_19</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CF_M06_AU21</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Apple Push Notification Service</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Messaging service for iOS devices.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>['AU_16', 'AU_26']</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>AU_19</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Apple Push Notification Service</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Firebase Cloud Messaging (FCM) for Android devices and Apple Push Notification Service (APNS) for iOS devices.</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>91</v>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>CF_M06_AU21</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>AU_18</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CF_M06_AU20</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Firebase Cloud Messaging</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Messaging service for Android devices.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>['AU_16', 'AU_26']</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>AU_18</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Firebase Cloud Messaging</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Firebase Cloud Messaging (FCM) for Android devices and Apple Push Notification Service (APNS) for iOS devices.</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>91</v>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>CF_M06_AU20</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>AU_07</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>CF_M06_AU08</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>A Javascript object that indicates an intention to modify the application state.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>AU_07</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> is a Javascript object that indicates an intention to modify the state of the application.</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>CF_M06_P02</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>CF_M06_AU08</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>AU_14</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>CF_M06_AU18</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Programming language developed by Microsoft, a superset of Javascript.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>AU_14</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>it is a programming language developed and maintained by Microsoft</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>CF_M06_AU18</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2855,7 +3377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2903,101 +3425,141 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>AU_16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>presentation layer, waapiti server</t>
-        </is>
-      </c>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Push Notification Service</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Via sockets es poden rebre els logs en temps real</t>
+          <t>Service responsible for delivering push notifications to devices.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CF_M06_AU30</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>CF_M06_AU21</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Apple Push Notification Service</t>
+        </is>
+      </c>
       <c r="H2" t="n">
-        <v>0.7084</v>
+        <v>0.9303</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_19</t>
+          <t>AU_20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>presentation layer, waapiti server</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aquesta última pestanya mostra un historial de reproducció del player. A més, es connecta també via socket amb el servidor i mostra logs en temps real.</t>
+          <t>Third-party companies that offer digital signage service/consulting using Waapiti technology.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CF_M06_AU30</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>CF_M06_AU08</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
       <c r="H3" t="n">
-        <v>0.7385</v>
+        <v>0.748</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>AU_24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>3-Layer Architecture</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>presentation layer, waapiti server</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>This architecture follows the 3-layer model: Presentation, Domain, and Data.</t>
+          <t>The application uses sockets to receive logs in real time from the server.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CF_M06_P01</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Three Layers</t>
-        </is>
-      </c>
+          <t>CF_M06_AU30</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.8511</v>
+        <v>0.7722</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AU_26</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>push notification service, mobile device, aws sns, firebase cloud messaging, apple push notification service</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>The Push Notification Service delivers push notifications to devices using AWS SNS, Firebase Cloud Messaging, and Apple Push Notification Service.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>CF_M06_AU21</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Apple Push Notification Service</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0.8616</v>
       </c>
     </row>
   </sheetData>
@@ -3011,7 +3573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3059,7 +3621,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CF_M06_AU10</t>
+          <t>CF_M06_AU11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3070,152 +3632,153 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>action, store</t>
+          <t>dispatcher, store</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>With the data obtained, the Dispatcher notifies the Stores that need to be modified, thus updating the components.</t>
+          <t>This is the central hub that manages all the data flow. It notifies the Stores when the state needs to be modified.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AU_08</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Dispatcher</t>
-        </is>
-      </c>
+          <t>AU_23</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.731</v>
+        <v>0.8439</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CF_M06_AU11</t>
+          <t>CF_M06_AU12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>dispatcher, store</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>As already mentioned, there are third-party companies that offer digital signage consulting using Waapiti technology. They are end users of this project.</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AU_01</t>
+          <t>AU_07</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Mobile Device</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>0.7607</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CF_M06_AU12</t>
+          <t>CF_M06_AU13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>User</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>presentation, user</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>As already mentioned, there are third-party companies that offer digital signage consulting using Waapiti technology. They are end users of this project.</t>
+          <t>Presentation: This is the layer that communicates with the user</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AU_07</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>Presentation Layer</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.7607</v>
+        <v>0.8952</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M06_AU13</t>
+          <t>CF_M06_AU23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>presentation, user</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Mobile Application</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Presentation: This is the layer that communicates with the user</t>
+          <t>The project “Development of a mobile application for a digital signage company”</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>AU_01</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Presentation Layer</t>
+          <t>Mobile Device</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.8952</v>
+        <v>0.8665</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CF_M06_AU16</t>
+          <t>CF_M06_AU24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Device</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jest</t>
+          <t>Player</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>is a testing framework for Javascript. It is also the libraryrecommended for React projects. [20]</t>
+          <t xml:space="preserve">these are computer equipment that act as an intermediary between the Waapiti platform and the audiovisual media itself, thus allowing the synchronization or reproduction of client
+content. </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -3229,13 +3792,13 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.6788</v>
+        <v>0.7835</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CF_M06_AU17</t>
+          <t>CF_M06_AU25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3245,69 +3808,70 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NodeJS</t>
+          <t>Redux</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>is a Javascript runtime environment that allows you to run it outside of the browser. In this case it is used to compile.</t>
+          <t>Redux [19] is a library used to manage application state. It is inspired by the Flux architecture, but with a simpler implementation.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AU_09</t>
+          <t>AU_10</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>React Native</t>
+          <t>React</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.679</v>
+        <v>0.7194</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CF_M06_AU18</t>
+          <t>CF_M06_AU26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>TypeScript</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>waapiti server, mobile application</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>it is a programming language developed and maintained by Microsoft</t>
+          <t>The requirement will be understood as complete if the communications between the server and the application use the minimum possible information.
+and authenticated.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AU_09</t>
+          <t>AU_27</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>React Native</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.6611</v>
+        <v>0.6449</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CF_M06_AU19</t>
+          <t>CF_M06_AU31</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3317,281 +3881,23 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NestJS</t>
+          <t>Socket</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>is a progressive NodeJS framework for creating efficient applications reliable and scalable backend entities.</t>
+          <t>the content according to the messages that it sends.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AU_09</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>React Native</t>
-        </is>
-      </c>
+          <t>AU_25</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>0.6944</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CF_M06_AU20</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Firebase Cloud Messaging</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Firebase Cloud Messaging (FCM) for Android devices and Apple Push Notification Service (APNS) for iOS devices.</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>AU_13</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>AWS SNS</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>0.6545</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>CF_M06_AU21</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Apple Push Notification Service</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Firebase Cloud Messaging (FCM) for Android devices and Apple Push Notification Service (APNS) for iOS devices.</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>AU_13</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>AWS SNS</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>0.7131999999999999</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>CF_M06_AU23</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Mobile Application</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>The project “Development of a mobile application for a digital signage company”</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>AU_01</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Mobile Device</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>0.8665</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>CF_M06_AU24</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Device</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Player</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">these are computer equipment that act as an intermediary between the Waapiti platform and the audiovisual media itself, thus allowing the synchronization or reproduction of client
-content. </t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>AU_07</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>0.7835</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>CF_M06_AU26</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>waapiti server, mobile application</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>The requirement will be understood as complete if the communications between the server and the application use the minimum possible information.
-and authenticated.</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>AU_14</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>HTTP</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>0.6449</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>CF_M06_AU28</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>waapiti server, data</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>It is the server responsible for communicating with the database and other services hosted on AWS.</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>AU_13</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>AWS SNS</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>0.6957</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>CF_M06_P01</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Architectural Pattern</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Three Layers</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>This architecture follows the 3-layer model</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>P_01</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>3-Layer Architecture</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>0.8511</v>
+        <v>0.6839</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/architecture/validation/CF_M06/run_1/CF_M06_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/validation/CF_M06/run_1/CF_M06_arch_eval.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,6 +440,11 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -456,7 +461,10 @@
       <c r="C2" t="n">
         <v>0.7778</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>0.8235</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -475,6 +483,9 @@
         <v>0.8276</v>
       </c>
       <c r="D3" t="n">
+        <v>0.8727</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.9572000000000001</v>
       </c>
     </row>
@@ -491,6 +502,9 @@
         <v>0.5714</v>
       </c>
       <c r="D4" t="n">
+        <v>0.6153999999999999</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.8875</v>
       </c>
     </row>
@@ -1221,14 +1235,11 @@
           <t>45</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>AU_03</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>Presentation</t>
@@ -1252,13 +1263,11 @@
           <t>CF_M06_P01</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>CF_M06_AU03</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1299,14 +1308,11 @@
           <t>45</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>AU_05</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>Data</t>
@@ -1330,13 +1336,11 @@
           <t>CF_M06_P01</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>CF_M06_AU05</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1357,7 +1361,6 @@
       <c r="D4" t="n">
         <v>0.8232</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1378,7 +1381,6 @@
           <t>['AU_03', 'AU_02']</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>AU_25</t>
@@ -1389,7 +1391,6 @@
           <t>presentation layer, waapiti server</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1408,7 +1409,6 @@
           <t>CF_M06_AU23, CF_M06_AU02</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>CF_M06_AU30</t>
@@ -1459,14 +1459,11 @@
           <t>48</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>P_03</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>Observer Pattern</t>
@@ -1490,13 +1487,11 @@
           <t>CF_M06_P02</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>CF_M06_P03</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1537,14 +1532,11 @@
           <t>49</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>P_04</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Decorator Pattern</t>
@@ -1568,13 +1560,11 @@
           <t>CF_M06_AU23</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>CF_M06_P04</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1615,14 +1605,11 @@
           <t>45</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>AU_04</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Domain</t>
@@ -1646,13 +1633,11 @@
           <t>CF_M06_P01</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>CF_M06_AU04</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1693,14 +1678,11 @@
           <t>45</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>P_01</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Three Layers</t>
@@ -1724,13 +1706,11 @@
           <t>CF_M06_AU23</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>CF_M06_P01</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1751,7 +1731,6 @@
       <c r="D9" t="n">
         <v>0.8976</v>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1772,7 +1751,6 @@
           <t>['AU_08', 'AU_06']</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>AU_23</t>
@@ -1783,7 +1761,6 @@
           <t>dispatcher, store</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1802,7 +1779,6 @@
           <t>CF_M06_AU08, CF_M06_AU07</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>CF_M06_AU10</t>
@@ -1833,7 +1809,6 @@
       <c r="D10" t="n">
         <v>0.9107</v>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1854,7 +1829,6 @@
           <t>['AU_02', 'AU_05']</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>AU_22</t>
@@ -1865,7 +1839,6 @@
           <t>waapiti server, data layer</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1884,7 +1857,6 @@
           <t>CF_M06_AU02, CF_M06_AU05</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>CF_M06_AU28</t>
@@ -1915,7 +1887,6 @@
       <c r="D11" t="n">
         <v>0.9185</v>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1936,7 +1907,6 @@
           <t>['AU_03', 'AU_02']</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>AU_21</t>
@@ -1947,7 +1917,6 @@
           <t>presentation layer, waapiti server</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1966,7 +1935,6 @@
           <t>CF_M06_AU01, CF_M06_AU02</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>CF_M06_AU27</t>
@@ -2017,14 +1985,11 @@
           <t>45</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>AU_01</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>Mobile device</t>
@@ -2043,14 +2008,11 @@
       <c r="P12" t="n">
         <v>45</v>
       </c>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>CF_M06_AU01</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2091,14 +2053,11 @@
           <t>51</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>AU_09</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>React Native</t>
@@ -2122,13 +2081,11 @@
           <t>CF_M06_AU23</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>CF_M06_AU06</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2169,14 +2126,11 @@
           <t>51</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>AU_10</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>React</t>
@@ -2200,13 +2154,11 @@
           <t>CF_M06_AU23</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>CF_M06_AU14</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2247,14 +2199,11 @@
           <t>49</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>P_05</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>Lazy Loading</t>
@@ -2278,13 +2227,11 @@
           <t>CF_M06_AU23</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>CF_M06_P05</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2325,14 +2272,11 @@
           <t>47</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>AU_08</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>Dispatcher</t>
@@ -2356,13 +2300,11 @@
           <t>CF_M06_P02</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>CF_M06_AU09</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2403,14 +2345,11 @@
           <t>51</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>AU_12</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>Jest</t>
@@ -2434,13 +2373,11 @@
           <t>CF_M06_AU23</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>CF_M06_AU16</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2486,13 +2423,11 @@
           <t>['AU_21']</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>AU_27</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>HTTP</t>
@@ -2516,13 +2451,11 @@
           <t>CF_M06_AU26</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>CF_M06_AU29</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2563,14 +2496,11 @@
           <t>45</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>AU_02</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>Waapiti Server</t>
@@ -2589,14 +2519,11 @@
       <c r="P19" t="n">
         <v>45</v>
       </c>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
           <t>CF_M06_AU02</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2637,14 +2564,11 @@
           <t>46</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>AU_06</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>Store</t>
@@ -2668,13 +2592,11 @@
           <t>CF_M06_P02</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>CF_M06_AU07</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2715,14 +2637,11 @@
           <t>51</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>AU_11</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>Expo</t>
@@ -2746,13 +2665,11 @@
           <t>CF_M06_AU23</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>CF_M06_AU15</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2793,14 +2710,11 @@
           <t>51</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>AU_13</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>NodeJS</t>
@@ -2819,14 +2733,11 @@
       <c r="P22" t="n">
         <v>51</v>
       </c>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>CF_M06_AU17</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2867,14 +2778,11 @@
           <t>52</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>AU_15</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>NestJS</t>
@@ -2893,14 +2801,11 @@
       <c r="P23" t="n">
         <v>51</v>
       </c>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
           <t>CF_M06_AU19</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2946,13 +2851,11 @@
           <t>['AU_16', 'AU_26']</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>AU_17</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>AWS SNS</t>
@@ -2971,14 +2874,11 @@
       <c r="P24" t="n">
         <v>92</v>
       </c>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
           <t>CF_M06_AU22</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3019,14 +2919,11 @@
           <t>46</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>P_02</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>Flux</t>
@@ -3050,13 +2947,11 @@
           <t>CF_M06_AU23</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
           <t>CF_M06_P02</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3102,13 +2997,11 @@
           <t>['AU_16', 'AU_26']</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>AU_19</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>Apple Push Notification Service</t>
@@ -3127,14 +3020,11 @@
       <c r="P26" t="n">
         <v>91</v>
       </c>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
           <t>CF_M06_AU21</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3180,13 +3070,11 @@
           <t>['AU_16', 'AU_26']</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>AU_18</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>Firebase Cloud Messaging</t>
@@ -3205,14 +3093,11 @@
       <c r="P27" t="n">
         <v>91</v>
       </c>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
           <t>CF_M06_AU20</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3253,14 +3138,11 @@
           <t>47</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>AU_07</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>Action</t>
@@ -3284,13 +3166,11 @@
           <t>CF_M06_P02</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
           <t>CF_M06_AU08</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3331,14 +3211,11 @@
           <t>51</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>AU_14</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
           <t>TypeScript</t>
@@ -3357,14 +3234,11 @@
       <c r="P29" t="n">
         <v>51</v>
       </c>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
           <t>CF_M06_AU18</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3438,7 +3312,6 @@
           <t>Push Notification Service</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Service responsible for delivering push notifications to devices.</t>
@@ -3474,7 +3347,6 @@
           <t>Partner</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Third-party companies that offer digital signage service/consulting using Waapiti technology.</t>
@@ -3505,7 +3377,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>presentation layer, waapiti server</t>
@@ -3521,7 +3392,6 @@
           <t>CF_M06_AU30</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>0.7722</v>
       </c>
@@ -3537,7 +3407,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>push notification service, mobile device, aws sns, firebase cloud messaging, apple push notification service</t>
@@ -3629,7 +3498,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>dispatcher, store</t>
@@ -3645,7 +3513,6 @@
           <t>AU_23</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>0.8439</v>
       </c>
@@ -3666,7 +3533,6 @@
           <t>User</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>As already mentioned, there are third-party companies that offer digital signage consulting using Waapiti technology. They are end users of this project.</t>
@@ -3697,7 +3563,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>presentation, user</t>
@@ -3738,7 +3603,6 @@
           <t>Mobile Application</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>The project “Development of a mobile application for a digital signage company”</t>
@@ -3774,7 +3638,6 @@
           <t>Player</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t xml:space="preserve">these are computer equipment that act as an intermediary between the Waapiti platform and the audiovisual media itself, thus allowing the synchronization or reproduction of client
@@ -3811,7 +3674,6 @@
           <t>Redux</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>Redux [19] is a library used to manage application state. It is inspired by the Flux architecture, but with a simpler implementation.</t>
@@ -3842,7 +3704,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>waapiti server, mobile application</t>
@@ -3884,7 +3745,6 @@
           <t>Socket</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>the content according to the messages that it sends.</t>
@@ -3895,7 +3755,6 @@
           <t>AU_25</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>0.6839</v>
       </c>
